--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/avg/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/avg/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -836,6 +836,117 @@
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.7,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.7,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>97.23</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>94.78</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>93.44</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.9,scale_th=0.7,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>86.37</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>97.09</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>29.94</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.01,type=avg</t>
         </is>
       </c>
     </row>

--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/avg/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/avg/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -947,6 +947,154 @@
       <c r="K16" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.01,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>51.19</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>93.31</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.2,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>28.37</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.3,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>93.42</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.4,type=avg</t>
         </is>
       </c>
     </row>
